--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +790,950 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125307795</v>
+      </c>
+      <c r="B3" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>595840</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6568129</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125307830</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>595862</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6568121</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125299351</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91032</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>595823</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6568104</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125307851</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rövarkulan, Rövarkulan, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>595930</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6568172</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125299483</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>595815</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6568124</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125307933</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595855</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6568188</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125307929</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>595843</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6568185</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125299454</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91032</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>595901</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6568158</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125307795</v>
+        <v>125299351</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>91032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,31 +805,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -838,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595840</v>
+        <v>595823</v>
       </c>
       <c r="R3" t="n">
-        <v>6568129</v>
+        <v>6568104</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125307830</v>
+        <v>125307795</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,31 +926,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -955,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595862</v>
+        <v>595840</v>
       </c>
       <c r="R4" t="n">
-        <v>6568121</v>
+        <v>6568129</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299351</v>
+        <v>125299483</v>
       </c>
       <c r="B5" t="n">
-        <v>91032</v>
+        <v>8447</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,35 +1043,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595823</v>
+        <v>595815</v>
       </c>
       <c r="R5" t="n">
-        <v>6568104</v>
+        <v>6568124</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,7 +1148,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125307851</v>
+        <v>125307933</v>
       </c>
       <c r="B6" t="n">
         <v>57529</v>
@@ -1184,19 +1184,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rövarkulan, Rövarkulan, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595930</v>
+        <v>595855</v>
       </c>
       <c r="R6" t="n">
-        <v>6568172</v>
+        <v>6568188</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125299483</v>
+        <v>125307830</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,31 +1277,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1310,13 +1310,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595815</v>
+        <v>595862</v>
       </c>
       <c r="R7" t="n">
-        <v>6568124</v>
+        <v>6568121</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125307933</v>
+        <v>125299454</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>91032</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,27 +1398,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1427,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595855</v>
+        <v>595901</v>
       </c>
       <c r="R8" t="n">
-        <v>6568188</v>
+        <v>6568158</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1462,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1616,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125299454</v>
+        <v>125307851</v>
       </c>
       <c r="B10" t="n">
-        <v>91032</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,43 +1636,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Rövarkulan, Rövarkulan, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595901</v>
+        <v>595930</v>
       </c>
       <c r="R10" t="n">
-        <v>6568158</v>
+        <v>6568172</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,6 +1734,123 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125307984</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rövarkulan, Rövarkulan, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>595899</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6568173</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125307795</v>
+        <v>125299483</v>
       </c>
       <c r="B4" t="n">
         <v>8447</v>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595840</v>
+        <v>595815</v>
       </c>
       <c r="R4" t="n">
-        <v>6568129</v>
+        <v>6568124</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299483</v>
+        <v>125307929</v>
       </c>
       <c r="B5" t="n">
         <v>8447</v>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595815</v>
+        <v>595843</v>
       </c>
       <c r="R5" t="n">
-        <v>6568124</v>
+        <v>6568185</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125307933</v>
+        <v>125307795</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,31 +1160,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595855</v>
+        <v>595840</v>
       </c>
       <c r="R6" t="n">
-        <v>6568188</v>
+        <v>6568129</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125307830</v>
+        <v>125307851</v>
       </c>
       <c r="B7" t="n">
         <v>57529</v>
@@ -1301,22 +1301,22 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Rövarkulan, Rövarkulan, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595862</v>
+        <v>595930</v>
       </c>
       <c r="R7" t="n">
-        <v>6568121</v>
+        <v>6568172</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125299454</v>
+        <v>125307933</v>
       </c>
       <c r="B8" t="n">
-        <v>91032</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,31 +1398,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1431,10 +1427,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595901</v>
+        <v>595855</v>
       </c>
       <c r="R8" t="n">
-        <v>6568158</v>
+        <v>6568188</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1466,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125307929</v>
+        <v>125299454</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
+        <v>91032</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,31 +1511,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595843</v>
+        <v>595901</v>
       </c>
       <c r="R9" t="n">
-        <v>6568185</v>
+        <v>6568158</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,7 +1620,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125307851</v>
+        <v>125307830</v>
       </c>
       <c r="B10" t="n">
         <v>57529</v>
@@ -1656,22 +1656,22 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rövarkulan, Rövarkulan, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595930</v>
+        <v>595862</v>
       </c>
       <c r="R10" t="n">
-        <v>6568172</v>
+        <v>6568121</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125299351</v>
+        <v>125307929</v>
       </c>
       <c r="B3" t="n">
-        <v>91032</v>
+        <v>8447</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,35 +805,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595823</v>
+        <v>595843</v>
       </c>
       <c r="R3" t="n">
-        <v>6568104</v>
+        <v>6568185</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1031,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125307929</v>
+        <v>125307851</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,43 +1039,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Rövarkulan, Rövarkulan, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595843</v>
+        <v>595930</v>
       </c>
       <c r="R5" t="n">
-        <v>6568185</v>
+        <v>6568172</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1111,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1117,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1265,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125307851</v>
+        <v>125299351</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>91032</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,42 +1277,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rövarkulan, Rövarkulan, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595930</v>
+        <v>595823</v>
       </c>
       <c r="R7" t="n">
-        <v>6568172</v>
+        <v>6568104</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125299351</v>
+        <v>125307933</v>
       </c>
       <c r="B7" t="n">
-        <v>91032</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,31 +1277,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1310,13 +1306,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595823</v>
+        <v>595855</v>
       </c>
       <c r="R7" t="n">
-        <v>6568104</v>
+        <v>6568188</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,7 +1341,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1351,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125307933</v>
+        <v>125299351</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>91032</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,27 +1394,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595855</v>
+        <v>595823</v>
       </c>
       <c r="R8" t="n">
-        <v>6568188</v>
+        <v>6568104</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125307929</v>
+        <v>125299351</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>91032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,31 +805,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -838,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595843</v>
+        <v>595823</v>
       </c>
       <c r="R3" t="n">
-        <v>6568185</v>
+        <v>6568104</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125299483</v>
+        <v>125307830</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,31 +926,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -955,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595815</v>
+        <v>595862</v>
       </c>
       <c r="R4" t="n">
-        <v>6568124</v>
+        <v>6568121</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125307851</v>
+        <v>125307929</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,43 +1043,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rövarkulan, Rövarkulan, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595930</v>
+        <v>595843</v>
       </c>
       <c r="R5" t="n">
-        <v>6568172</v>
+        <v>6568185</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1107,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125307795</v>
+        <v>125299454</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>91032</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,31 +1160,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1189,13 +1197,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595840</v>
+        <v>595901</v>
       </c>
       <c r="R6" t="n">
-        <v>6568129</v>
+        <v>6568158</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1378,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125299351</v>
+        <v>125307851</v>
       </c>
       <c r="B8" t="n">
-        <v>91032</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,46 +1402,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Rövarkulan, Rövarkulan, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595823</v>
+        <v>595930</v>
       </c>
       <c r="R8" t="n">
-        <v>6568104</v>
+        <v>6568172</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125299454</v>
+        <v>125307795</v>
       </c>
       <c r="B9" t="n">
-        <v>91032</v>
+        <v>8447</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,35 +1515,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1548,13 +1548,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595901</v>
+        <v>595840</v>
       </c>
       <c r="R9" t="n">
-        <v>6568158</v>
+        <v>6568129</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125307830</v>
+        <v>125299483</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,31 +1632,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1665,13 +1665,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595862</v>
+        <v>595815</v>
       </c>
       <c r="R10" t="n">
-        <v>6568121</v>
+        <v>6568124</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124915494</v>
       </c>
       <c r="B2" t="n">
-        <v>57519</v>
+        <v>57648</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125299351</v>
+        <v>125307933</v>
       </c>
       <c r="B3" t="n">
-        <v>91032</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,31 +809,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595823</v>
+        <v>595855</v>
       </c>
       <c r="R3" t="n">
-        <v>6568104</v>
+        <v>6568188</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125307830</v>
+        <v>125307929</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,31 +922,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595862</v>
+        <v>595843</v>
       </c>
       <c r="R4" t="n">
-        <v>6568121</v>
+        <v>6568185</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125307929</v>
+        <v>125307830</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>57632</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,31 +1039,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595843</v>
+        <v>595862</v>
       </c>
       <c r="R5" t="n">
-        <v>6568185</v>
+        <v>6568121</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1117,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,7 +1147,7 @@
         <v>125299454</v>
       </c>
       <c r="B6" t="n">
-        <v>91032</v>
+        <v>91186</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1269,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125307933</v>
+        <v>125299351</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>91186</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,27 +1281,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595855</v>
+        <v>595823</v>
       </c>
       <c r="R7" t="n">
-        <v>6568188</v>
+        <v>6568104</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,7 +1389,7 @@
         <v>125307851</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125307933</v>
+        <v>125307795</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
+        <v>8447</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,31 +805,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595855</v>
+        <v>595840</v>
       </c>
       <c r="R3" t="n">
-        <v>6568188</v>
+        <v>6568129</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125307929</v>
+        <v>125307851</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>57632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,43 +922,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Rövarkulan, Rövarkulan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595843</v>
+        <v>595930</v>
       </c>
       <c r="R4" t="n">
-        <v>6568185</v>
+        <v>6568172</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125307830</v>
+        <v>125299454</v>
       </c>
       <c r="B5" t="n">
-        <v>57632</v>
+        <v>91186</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,27 +1043,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1072,13 +1076,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595862</v>
+        <v>595901</v>
       </c>
       <c r="R5" t="n">
-        <v>6568121</v>
+        <v>6568158</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125299454</v>
+        <v>125307933</v>
       </c>
       <c r="B6" t="n">
-        <v>91186</v>
+        <v>57632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,31 +1164,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595901</v>
+        <v>595855</v>
       </c>
       <c r="R6" t="n">
-        <v>6568158</v>
+        <v>6568188</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1386,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125307851</v>
+        <v>125307929</v>
       </c>
       <c r="B8" t="n">
-        <v>57632</v>
+        <v>8447</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,43 +1398,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rövarkulan, Rövarkulan, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595930</v>
+        <v>595843</v>
       </c>
       <c r="R8" t="n">
-        <v>6568172</v>
+        <v>6568185</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,7 +1503,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125307795</v>
+        <v>125299483</v>
       </c>
       <c r="B9" t="n">
         <v>8447</v>
@@ -1548,13 +1548,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595840</v>
+        <v>595815</v>
       </c>
       <c r="R9" t="n">
-        <v>6568129</v>
+        <v>6568124</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125299483</v>
+        <v>125307830</v>
       </c>
       <c r="B10" t="n">
-        <v>8447</v>
+        <v>57632</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,31 +1632,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1665,13 +1665,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595815</v>
+        <v>595862</v>
       </c>
       <c r="R10" t="n">
-        <v>6568124</v>
+        <v>6568121</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1386,7 +1386,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125307929</v>
+        <v>125299483</v>
       </c>
       <c r="B8" t="n">
         <v>8447</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595843</v>
+        <v>595815</v>
       </c>
       <c r="R8" t="n">
-        <v>6568185</v>
+        <v>6568124</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,7 +1503,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125299483</v>
+        <v>125307929</v>
       </c>
       <c r="B9" t="n">
         <v>8447</v>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595815</v>
+        <v>595843</v>
       </c>
       <c r="R9" t="n">
-        <v>6568124</v>
+        <v>6568185</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1012,38 +1012,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125307929</v>
+        <v>125299351</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>91240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595843</v>
+        <v>595823</v>
       </c>
       <c r="R5" t="n">
-        <v>6568185</v>
+        <v>6568104</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125307795</v>
+        <v>125307929</v>
       </c>
       <c r="B6" t="n">
         <v>8447</v>
@@ -1164,13 +1168,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595840</v>
+        <v>595843</v>
       </c>
       <c r="R6" t="n">
-        <v>6568129</v>
+        <v>6568185</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,42 +1240,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125299351</v>
+        <v>125307795</v>
       </c>
       <c r="B7" t="n">
-        <v>91240</v>
+        <v>8447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595823</v>
+        <v>595840</v>
       </c>
       <c r="R7" t="n">
-        <v>6568104</v>
+        <v>6568129</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1012,42 +1012,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299351</v>
+        <v>125307929</v>
       </c>
       <c r="B5" t="n">
-        <v>91240</v>
+        <v>8447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595823</v>
+        <v>595843</v>
       </c>
       <c r="R5" t="n">
-        <v>6568104</v>
+        <v>6568185</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125307929</v>
+        <v>125307795</v>
       </c>
       <c r="B6" t="n">
         <v>8447</v>
@@ -1168,13 +1164,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595843</v>
+        <v>595840</v>
       </c>
       <c r="R6" t="n">
-        <v>6568185</v>
+        <v>6568129</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1209,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,38 +1236,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125307795</v>
+        <v>125299351</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>91247</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595840</v>
+        <v>595823</v>
       </c>
       <c r="R7" t="n">
-        <v>6568129</v>
+        <v>6568104</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1467,7 +1467,7 @@
         <v>125299454</v>
       </c>
       <c r="B9" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1802,6 +1802,565 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125971359</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90611</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>595742</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125971148</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>595710</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125971411</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>595744</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6568074</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125961828</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58019</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>595744</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6568074</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125971393</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>595742</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1012,38 +1012,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125307929</v>
+        <v>125299351</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>91247</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595843</v>
+        <v>595823</v>
       </c>
       <c r="R5" t="n">
-        <v>6568185</v>
+        <v>6568104</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125307795</v>
+        <v>125307929</v>
       </c>
       <c r="B6" t="n">
         <v>8447</v>
@@ -1164,13 +1168,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595840</v>
+        <v>595843</v>
       </c>
       <c r="R6" t="n">
-        <v>6568129</v>
+        <v>6568185</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,42 +1240,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125299351</v>
+        <v>125307795</v>
       </c>
       <c r="B7" t="n">
-        <v>91247</v>
+        <v>8447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595823</v>
+        <v>595840</v>
       </c>
       <c r="R7" t="n">
-        <v>6568104</v>
+        <v>6568129</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1807,7 +1807,7 @@
         <v>125971359</v>
       </c>
       <c r="B12" t="n">
-        <v>90611</v>
+        <v>90612</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,32 +1916,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125971148</v>
+        <v>125971411</v>
       </c>
       <c r="B13" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595710</v>
+        <v>595744</v>
       </c>
       <c r="R13" t="n">
-        <v>6568136</v>
+        <v>6568074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125971411</v>
+        <v>125971148</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595744</v>
+        <v>595710</v>
       </c>
       <c r="R14" t="n">
-        <v>6568074</v>
+        <v>6568136</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2143,7 +2143,7 @@
         <v>125961828</v>
       </c>
       <c r="B15" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1012,42 +1012,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299351</v>
+        <v>125307929</v>
       </c>
       <c r="B5" t="n">
-        <v>91247</v>
+        <v>8447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595823</v>
+        <v>595843</v>
       </c>
       <c r="R5" t="n">
-        <v>6568104</v>
+        <v>6568185</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1124,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125307929</v>
+        <v>125307795</v>
       </c>
       <c r="B6" t="n">
         <v>8447</v>
@@ -1168,13 +1164,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595843</v>
+        <v>595840</v>
       </c>
       <c r="R6" t="n">
-        <v>6568185</v>
+        <v>6568129</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1209,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,38 +1236,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125307795</v>
+        <v>125299351</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>91248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595840</v>
+        <v>595823</v>
       </c>
       <c r="R7" t="n">
-        <v>6568129</v>
+        <v>6568104</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1467,7 +1467,7 @@
         <v>125299454</v>
       </c>
       <c r="B9" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1916,32 +1916,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125971411</v>
+        <v>125971148</v>
       </c>
       <c r="B13" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595744</v>
+        <v>595710</v>
       </c>
       <c r="R13" t="n">
-        <v>6568074</v>
+        <v>6568136</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125971148</v>
+        <v>125971411</v>
       </c>
       <c r="B14" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595710</v>
+        <v>595744</v>
       </c>
       <c r="R14" t="n">
-        <v>6568136</v>
+        <v>6568074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1807,7 +1807,7 @@
         <v>125971359</v>
       </c>
       <c r="B12" t="n">
-        <v>90612</v>
+        <v>90616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1807,7 +1807,7 @@
         <v>125971359</v>
       </c>
       <c r="B12" t="n">
-        <v>90616</v>
+        <v>90618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,32 +1916,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125971148</v>
+        <v>125971411</v>
       </c>
       <c r="B13" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595710</v>
+        <v>595744</v>
       </c>
       <c r="R13" t="n">
-        <v>6568136</v>
+        <v>6568074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125971411</v>
+        <v>125971148</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595744</v>
+        <v>595710</v>
       </c>
       <c r="R14" t="n">
-        <v>6568074</v>
+        <v>6568136</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2143,7 +2143,7 @@
         <v>125961828</v>
       </c>
       <c r="B15" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1916,32 +1916,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125971411</v>
+        <v>125971148</v>
       </c>
       <c r="B13" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595744</v>
+        <v>595710</v>
       </c>
       <c r="R13" t="n">
-        <v>6568074</v>
+        <v>6568136</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125971148</v>
+        <v>125971411</v>
       </c>
       <c r="B14" t="n">
-        <v>57649</v>
+        <v>8447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595710</v>
+        <v>595744</v>
       </c>
       <c r="R14" t="n">
-        <v>6568136</v>
+        <v>6568074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1807,7 +1807,7 @@
         <v>125971359</v>
       </c>
       <c r="B12" t="n">
-        <v>90618</v>
+        <v>90620</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1807,7 +1807,7 @@
         <v>125971359</v>
       </c>
       <c r="B12" t="n">
-        <v>90620</v>
+        <v>90622</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1916,32 +1916,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125971148</v>
+        <v>125971411</v>
       </c>
       <c r="B13" t="n">
-        <v>57649</v>
+        <v>8447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595710</v>
+        <v>595744</v>
       </c>
       <c r="R13" t="n">
-        <v>6568136</v>
+        <v>6568074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125971411</v>
+        <v>125971148</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>57649</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595744</v>
+        <v>595710</v>
       </c>
       <c r="R14" t="n">
-        <v>6568074</v>
+        <v>6568136</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1807,7 +1807,7 @@
         <v>125971359</v>
       </c>
       <c r="B12" t="n">
-        <v>90622</v>
+        <v>90626</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,32 +1916,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125971411</v>
+        <v>125971148</v>
       </c>
       <c r="B13" t="n">
-        <v>8447</v>
+        <v>57653</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595744</v>
+        <v>595710</v>
       </c>
       <c r="R13" t="n">
-        <v>6568074</v>
+        <v>6568136</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125971148</v>
+        <v>125971411</v>
       </c>
       <c r="B14" t="n">
-        <v>57649</v>
+        <v>8447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595710</v>
+        <v>595744</v>
       </c>
       <c r="R14" t="n">
-        <v>6568136</v>
+        <v>6568074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2143,7 +2143,7 @@
         <v>125961828</v>
       </c>
       <c r="B15" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1916,32 +1916,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125971148</v>
+        <v>125971411</v>
       </c>
       <c r="B13" t="n">
-        <v>57653</v>
+        <v>8447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595710</v>
+        <v>595744</v>
       </c>
       <c r="R13" t="n">
-        <v>6568136</v>
+        <v>6568074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125971411</v>
+        <v>125971148</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>57653</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595744</v>
+        <v>595710</v>
       </c>
       <c r="R14" t="n">
-        <v>6568074</v>
+        <v>6568136</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1916,32 +1916,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125971411</v>
+        <v>125971148</v>
       </c>
       <c r="B13" t="n">
-        <v>8447</v>
+        <v>57653</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595744</v>
+        <v>595710</v>
       </c>
       <c r="R13" t="n">
-        <v>6568074</v>
+        <v>6568136</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125971148</v>
+        <v>125971411</v>
       </c>
       <c r="B14" t="n">
-        <v>57653</v>
+        <v>8447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595710</v>
+        <v>595744</v>
       </c>
       <c r="R14" t="n">
-        <v>6568136</v>
+        <v>6568074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1807,7 +1807,7 @@
         <v>125971359</v>
       </c>
       <c r="B12" t="n">
-        <v>90626</v>
+        <v>90629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>125971148</v>
       </c>
       <c r="B13" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>125961828</v>
       </c>
       <c r="B15" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1916,32 +1916,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125971148</v>
+        <v>125971411</v>
       </c>
       <c r="B13" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595710</v>
+        <v>595744</v>
       </c>
       <c r="R13" t="n">
-        <v>6568136</v>
+        <v>6568074</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125971411</v>
+        <v>125971148</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595744</v>
+        <v>595710</v>
       </c>
       <c r="R14" t="n">
-        <v>6568074</v>
+        <v>6568136</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1916,32 +1916,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125971411</v>
+        <v>125971148</v>
       </c>
       <c r="B13" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595744</v>
+        <v>595710</v>
       </c>
       <c r="R13" t="n">
-        <v>6568074</v>
+        <v>6568136</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125971148</v>
+        <v>125971411</v>
       </c>
       <c r="B14" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595710</v>
+        <v>595744</v>
       </c>
       <c r="R14" t="n">
-        <v>6568136</v>
+        <v>6568074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2361,6 +2361,123 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127675667</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>595849</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6568116</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Landhöjningsblandskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Pia Ölvebro</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Pia Ölvebro</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -2366,7 +2366,7 @@
         <v>127675667</v>
       </c>
       <c r="B17" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -2366,7 +2366,7 @@
         <v>127675667</v>
       </c>
       <c r="B17" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -2366,7 +2366,7 @@
         <v>127675667</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125307933</v>
+        <v>124915494</v>
       </c>
       <c r="B2" t="n">
         <v>57648</v>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,25 +703,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Långdal, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595855</v>
+        <v>595823</v>
       </c>
       <c r="R2" t="n">
-        <v>6568188</v>
+        <v>6568114</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:37</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:37</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +776,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Pia Ölvebro</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Pia Ölvebro</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125307929</v>
+        <v>125299483</v>
       </c>
       <c r="B3" t="n">
         <v>8447</v>
@@ -827,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595843</v>
+        <v>595815</v>
       </c>
       <c r="R3" t="n">
-        <v>6568185</v>
+        <v>6568124</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,53 +900,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125307851</v>
+        <v>125307795</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rövarkulan, Rövarkulan, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595930</v>
+        <v>595840</v>
       </c>
       <c r="R4" t="n">
-        <v>6568172</v>
+        <v>6568129</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299454</v>
+        <v>125299351</v>
       </c>
       <c r="B5" t="n">
         <v>91248</v>
@@ -1041,7 +1042,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1055,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595901</v>
+        <v>595823</v>
       </c>
       <c r="R5" t="n">
-        <v>6568158</v>
+        <v>6568104</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,53 +1128,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125307984</v>
+        <v>125307830</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rövarkulan, Rövarkulan, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595899</v>
+        <v>595862</v>
       </c>
       <c r="R6" t="n">
-        <v>6568173</v>
+        <v>6568121</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,6 +1237,463 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125971359</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90834</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>595742</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125971148</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595710</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125971393</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>595742</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127675667</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>595849</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6568116</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Landhöjningsblandskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pia Ölvebro</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pia Ölvebro</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124915494</v>
+        <v>125307933</v>
       </c>
       <c r="B2" t="n">
         <v>57648</v>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,36 +703,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långdal, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595823</v>
+        <v>595855</v>
       </c>
       <c r="R2" t="n">
-        <v>6568114</v>
+        <v>6568188</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Pia Ölvebro</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pia Ölvebro</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125299483</v>
+        <v>125307929</v>
       </c>
       <c r="B3" t="n">
         <v>8447</v>
@@ -828,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595815</v>
+        <v>595843</v>
       </c>
       <c r="R3" t="n">
-        <v>6568124</v>
+        <v>6568185</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -863,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,53 +899,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125307795</v>
+        <v>125307851</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Rövarkulan, Rövarkulan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595840</v>
+        <v>595930</v>
       </c>
       <c r="R4" t="n">
-        <v>6568129</v>
+        <v>6568172</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299351</v>
+        <v>125299454</v>
       </c>
       <c r="B5" t="n">
         <v>91248</v>
@@ -1042,7 +1041,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1056,13 +1055,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595823</v>
+        <v>595901</v>
       </c>
       <c r="R5" t="n">
-        <v>6568104</v>
+        <v>6568158</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,53 +1127,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125307830</v>
+        <v>125307984</v>
       </c>
       <c r="B6" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Rövarkulan, Rövarkulan, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595862</v>
+        <v>595899</v>
       </c>
       <c r="R6" t="n">
-        <v>6568121</v>
+        <v>6568173</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,463 +1236,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>125971359</v>
-      </c>
-      <c r="B7" t="n">
-        <v>90834</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5685</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Gullgröppa</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Pseudomerulius aureus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Långdal, Långdal, Srm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>595742</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6568136</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>125971148</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57654</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Långdal, Långdal, Srm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>595710</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6568136</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>125971393</v>
-      </c>
-      <c r="B9" t="n">
-        <v>8447</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Långdal, Långdal, Srm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>595742</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6568136</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>127675667</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57670</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Långdal, Srm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>595849</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6568116</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Landhöjningsblandskog</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Pia Ölvebro</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Pia Ölvebro</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125307933</v>
+        <v>124915494</v>
       </c>
       <c r="B2" t="n">
         <v>57648</v>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,25 +703,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Långdal, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595855</v>
+        <v>595823</v>
       </c>
       <c r="R2" t="n">
-        <v>6568188</v>
+        <v>6568114</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:37</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:37</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +776,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Pia Ölvebro</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Pia Ölvebro</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125307929</v>
+        <v>125299483</v>
       </c>
       <c r="B3" t="n">
         <v>8447</v>
@@ -827,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595843</v>
+        <v>595815</v>
       </c>
       <c r="R3" t="n">
-        <v>6568185</v>
+        <v>6568124</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,53 +900,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125307851</v>
+        <v>125307795</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rövarkulan, Rövarkulan, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595930</v>
+        <v>595840</v>
       </c>
       <c r="R4" t="n">
-        <v>6568172</v>
+        <v>6568129</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299454</v>
+        <v>125299351</v>
       </c>
       <c r="B5" t="n">
         <v>91248</v>
@@ -1041,7 +1042,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1055,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595901</v>
+        <v>595823</v>
       </c>
       <c r="R5" t="n">
-        <v>6568158</v>
+        <v>6568104</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,53 +1128,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125307984</v>
+        <v>125307830</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rövarkulan, Rövarkulan, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595899</v>
+        <v>595862</v>
       </c>
       <c r="R6" t="n">
-        <v>6568173</v>
+        <v>6568121</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,6 +1237,463 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125971359</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90848</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>595742</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125971148</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595710</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125971393</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>595742</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127675667</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>595849</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6568116</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Landhöjningsblandskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pia Ölvebro</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pia Ölvebro</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124915494</v>
+        <v>125307933</v>
       </c>
       <c r="B2" t="n">
         <v>57648</v>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,36 +703,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långdal, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595823</v>
+        <v>595855</v>
       </c>
       <c r="R2" t="n">
-        <v>6568114</v>
+        <v>6568188</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Pia Ölvebro</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pia Ölvebro</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125299483</v>
+        <v>125307929</v>
       </c>
       <c r="B3" t="n">
         <v>8447</v>
@@ -828,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595815</v>
+        <v>595843</v>
       </c>
       <c r="R3" t="n">
-        <v>6568124</v>
+        <v>6568185</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -863,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,53 +899,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125307795</v>
+        <v>125307851</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Rövarkulan, Rövarkulan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595840</v>
+        <v>595930</v>
       </c>
       <c r="R4" t="n">
-        <v>6568129</v>
+        <v>6568172</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299351</v>
+        <v>125299454</v>
       </c>
       <c r="B5" t="n">
         <v>91248</v>
@@ -1042,7 +1041,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1056,13 +1055,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595823</v>
+        <v>595901</v>
       </c>
       <c r="R5" t="n">
-        <v>6568104</v>
+        <v>6568158</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,53 +1127,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125307830</v>
+        <v>125307984</v>
       </c>
       <c r="B6" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Rövarkulan, Rövarkulan, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595862</v>
+        <v>595899</v>
       </c>
       <c r="R6" t="n">
-        <v>6568121</v>
+        <v>6568173</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,463 +1236,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>125971359</v>
-      </c>
-      <c r="B7" t="n">
-        <v>90848</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5685</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Gullgröppa</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Pseudomerulius aureus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Långdal, Långdal, Srm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>595742</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6568136</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>125971148</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57654</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Långdal, Långdal, Srm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>595710</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6568136</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>125971393</v>
-      </c>
-      <c r="B9" t="n">
-        <v>8447</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Långdal, Långdal, Srm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>595742</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6568136</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>127675667</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57670</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Långdal, Srm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>595849</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6568116</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Landhöjningsblandskog</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Pia Ölvebro</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Pia Ölvebro</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125307933</v>
+        <v>124915494</v>
       </c>
       <c r="B2" t="n">
         <v>57648</v>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,25 +703,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Långdal, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595855</v>
+        <v>595823</v>
       </c>
       <c r="R2" t="n">
-        <v>6568188</v>
+        <v>6568114</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:37</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:37</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +776,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Pia Ölvebro</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Pia Ölvebro</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125307929</v>
+        <v>125299483</v>
       </c>
       <c r="B3" t="n">
         <v>8447</v>
@@ -827,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595843</v>
+        <v>595815</v>
       </c>
       <c r="R3" t="n">
-        <v>6568185</v>
+        <v>6568124</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,53 +900,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125307851</v>
+        <v>125307795</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rövarkulan, Rövarkulan, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595930</v>
+        <v>595840</v>
       </c>
       <c r="R4" t="n">
-        <v>6568172</v>
+        <v>6568129</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299454</v>
+        <v>125299351</v>
       </c>
       <c r="B5" t="n">
         <v>91248</v>
@@ -1041,7 +1042,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1055,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595901</v>
+        <v>595823</v>
       </c>
       <c r="R5" t="n">
-        <v>6568158</v>
+        <v>6568104</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,53 +1128,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125307984</v>
+        <v>125307830</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rövarkulan, Rövarkulan, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595899</v>
+        <v>595862</v>
       </c>
       <c r="R6" t="n">
-        <v>6568173</v>
+        <v>6568121</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,6 +1237,463 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125971359</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90849</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>595742</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125971148</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595710</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125971393</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>595742</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127675667</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>595849</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6568116</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Landhöjningsblandskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pia Ölvebro</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pia Ölvebro</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124915494</v>
+        <v>125307933</v>
       </c>
       <c r="B2" t="n">
         <v>57648</v>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,36 +703,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långdal, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595823</v>
+        <v>595855</v>
       </c>
       <c r="R2" t="n">
-        <v>6568114</v>
+        <v>6568188</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Pia Ölvebro</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pia Ölvebro</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125299483</v>
+        <v>125307929</v>
       </c>
       <c r="B3" t="n">
         <v>8447</v>
@@ -828,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595815</v>
+        <v>595843</v>
       </c>
       <c r="R3" t="n">
-        <v>6568124</v>
+        <v>6568185</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -863,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,53 +899,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125307795</v>
+        <v>125307851</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Rövarkulan, Rövarkulan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595840</v>
+        <v>595930</v>
       </c>
       <c r="R4" t="n">
-        <v>6568129</v>
+        <v>6568172</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299351</v>
+        <v>125299454</v>
       </c>
       <c r="B5" t="n">
         <v>91248</v>
@@ -1042,7 +1041,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1056,13 +1055,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595823</v>
+        <v>595901</v>
       </c>
       <c r="R5" t="n">
-        <v>6568104</v>
+        <v>6568158</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,53 +1127,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125307830</v>
+        <v>125307984</v>
       </c>
       <c r="B6" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Rövarkulan, Rövarkulan, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595862</v>
+        <v>595899</v>
       </c>
       <c r="R6" t="n">
-        <v>6568121</v>
+        <v>6568173</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,463 +1236,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>125971359</v>
-      </c>
-      <c r="B7" t="n">
-        <v>90849</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5685</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Gullgröppa</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Pseudomerulius aureus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Långdal, Långdal, Srm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>595742</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6568136</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>125971148</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57654</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Långdal, Långdal, Srm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>595710</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6568136</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>125971393</v>
-      </c>
-      <c r="B9" t="n">
-        <v>8447</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Långdal, Långdal, Srm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>595742</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6568136</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>127675667</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57670</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Långdal, Srm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>595849</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6568116</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Landhöjningsblandskog</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Pia Ölvebro</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Pia Ölvebro</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125307933</v>
+        <v>124915494</v>
       </c>
       <c r="B2" t="n">
         <v>57648</v>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,25 +703,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Långdal, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595855</v>
+        <v>595823</v>
       </c>
       <c r="R2" t="n">
-        <v>6568188</v>
+        <v>6568114</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:37</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:37</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +776,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Pia Ölvebro</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Pia Ölvebro</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125307929</v>
+        <v>125299483</v>
       </c>
       <c r="B3" t="n">
         <v>8447</v>
@@ -827,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595843</v>
+        <v>595815</v>
       </c>
       <c r="R3" t="n">
-        <v>6568185</v>
+        <v>6568124</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,53 +900,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125307851</v>
+        <v>125307795</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rövarkulan, Rövarkulan, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595930</v>
+        <v>595840</v>
       </c>
       <c r="R4" t="n">
-        <v>6568172</v>
+        <v>6568129</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299454</v>
+        <v>125299351</v>
       </c>
       <c r="B5" t="n">
         <v>91248</v>
@@ -1041,7 +1042,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1055,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595901</v>
+        <v>595823</v>
       </c>
       <c r="R5" t="n">
-        <v>6568158</v>
+        <v>6568104</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,53 +1128,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125307984</v>
+        <v>125307830</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rövarkulan, Rövarkulan, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595899</v>
+        <v>595862</v>
       </c>
       <c r="R6" t="n">
-        <v>6568173</v>
+        <v>6568121</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,6 +1237,463 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125971359</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90876</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>595742</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125971148</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595710</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125971393</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>595742</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127675667</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>595849</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6568116</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Landhöjningsblandskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pia Ölvebro</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pia Ölvebro</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>125971359</v>
       </c>
       <c r="B7" t="n">
-        <v>90876</v>
+        <v>90886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>125971359</v>
       </c>
       <c r="B7" t="n">
-        <v>90886</v>
+        <v>90890</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124915494</v>
+        <v>125307933</v>
       </c>
       <c r="B2" t="n">
         <v>57648</v>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,36 +703,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långdal, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595823</v>
+        <v>595855</v>
       </c>
       <c r="R2" t="n">
-        <v>6568114</v>
+        <v>6568188</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Pia Ölvebro</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pia Ölvebro</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125299483</v>
+        <v>125307929</v>
       </c>
       <c r="B3" t="n">
         <v>8447</v>
@@ -828,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595815</v>
+        <v>595843</v>
       </c>
       <c r="R3" t="n">
-        <v>6568124</v>
+        <v>6568185</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -863,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,53 +899,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125307795</v>
+        <v>125307851</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Rövarkulan, Rövarkulan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595840</v>
+        <v>595930</v>
       </c>
       <c r="R4" t="n">
-        <v>6568129</v>
+        <v>6568172</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299351</v>
+        <v>125299454</v>
       </c>
       <c r="B5" t="n">
         <v>91248</v>
@@ -1042,7 +1041,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1056,13 +1055,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595823</v>
+        <v>595901</v>
       </c>
       <c r="R5" t="n">
-        <v>6568104</v>
+        <v>6568158</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,53 +1127,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125307830</v>
+        <v>125307984</v>
       </c>
       <c r="B6" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Rövarkulan, Rövarkulan, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595862</v>
+        <v>595899</v>
       </c>
       <c r="R6" t="n">
-        <v>6568121</v>
+        <v>6568173</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,463 +1236,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>125971359</v>
-      </c>
-      <c r="B7" t="n">
-        <v>90890</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5685</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Gullgröppa</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Pseudomerulius aureus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Långdal, Långdal, Srm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>595742</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6568136</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>125971148</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57654</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Långdal, Långdal, Srm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>595710</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6568136</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>125971393</v>
-      </c>
-      <c r="B9" t="n">
-        <v>8447</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Långdal, Långdal, Srm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>595742</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6568136</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Kent Hellström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>127675667</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57670</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Långdal, Srm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>595849</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6568116</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Eskilstuna</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Ärla</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-08-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Landhöjningsblandskog</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Pia Ölvebro</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Pia Ölvebro</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125307933</v>
+        <v>124915494</v>
       </c>
       <c r="B2" t="n">
         <v>57648</v>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,25 +703,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långdal, Långdal, Srm</t>
+          <t>Långdal, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595855</v>
+        <v>595823</v>
       </c>
       <c r="R2" t="n">
-        <v>6568188</v>
+        <v>6568114</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:37</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:37</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +776,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Pia Ölvebro</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Pia Ölvebro</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125307929</v>
+        <v>125299483</v>
       </c>
       <c r="B3" t="n">
         <v>8447</v>
@@ -827,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595843</v>
+        <v>595815</v>
       </c>
       <c r="R3" t="n">
-        <v>6568185</v>
+        <v>6568124</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,53 +900,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125307851</v>
+        <v>125307795</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>8447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rövarkulan, Rövarkulan, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595930</v>
+        <v>595840</v>
       </c>
       <c r="R4" t="n">
-        <v>6568172</v>
+        <v>6568129</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125299454</v>
+        <v>125299351</v>
       </c>
       <c r="B5" t="n">
         <v>91248</v>
@@ -1041,7 +1042,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1055,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595901</v>
+        <v>595823</v>
       </c>
       <c r="R5" t="n">
-        <v>6568158</v>
+        <v>6568104</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,53 +1128,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125307984</v>
+        <v>125307830</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>57648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rövarkulan, Rövarkulan, Srm</t>
+          <t>Långdal, Långdal, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595899</v>
+        <v>595862</v>
       </c>
       <c r="R6" t="n">
-        <v>6568173</v>
+        <v>6568121</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,6 +1237,463 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125971359</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90890</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>595742</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125971148</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595710</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125971393</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>595742</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6568136</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127675667</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>595849</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6568116</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Landhöjningsblandskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pia Ölvebro</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pia Ölvebro</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1700,7 +1700,7 @@
         <v>129084031</v>
       </c>
       <c r="B11" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1700,7 +1700,7 @@
         <v>129084031</v>
       </c>
       <c r="B11" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1810,6 +1810,123 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130010028</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>595854</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6568108</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska hackspår omgivna av typiskt bortslitna och ivägkastade träflisor.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1927,6 +1927,790 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130024426</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57753</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>595678</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6568156</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130024488</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58111</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>595717</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6568220</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Liten del av tallbarrskog där andelen gran är stor.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130024428</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57734</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>595743</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6568106</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosöksspår i myrstack.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130024418</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57753</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>595824</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6568125</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosökande i tall, på död gren. Blandskog, dominerad av tallar på 100-200 år.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130024445</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57734</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>595762</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6568161</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosöksspår i myrstack.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130024435</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57734</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långdal, Långdal, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>595695</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6568104</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosöksspår i myrstack.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -2479,7 +2479,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130024445</v>
+        <v>130024435</v>
       </c>
       <c r="B17" t="n">
         <v>57734</v>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595762</v>
+        <v>595695</v>
       </c>
       <c r="R17" t="n">
-        <v>6568161</v>
+        <v>6568104</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2596,7 +2596,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130024435</v>
+        <v>130024445</v>
       </c>
       <c r="B18" t="n">
         <v>57734</v>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595695</v>
+        <v>595762</v>
       </c>
       <c r="R18" t="n">
-        <v>6568104</v>
+        <v>6568161</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -2068,7 +2068,7 @@
         <v>130024488</v>
       </c>
       <c r="B14" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 18484-2025 artfynd.xlsx
+++ b/artfynd/A 18484-2025 artfynd.xlsx
@@ -1815,7 +1815,7 @@
         <v>130010028</v>
       </c>
       <c r="B12" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>130024426</v>
       </c>
       <c r="B13" t="n">
-        <v>57754</v>
+        <v>57839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>130024488</v>
       </c>
       <c r="B14" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>130024428</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>57820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>130024418</v>
       </c>
       <c r="B16" t="n">
-        <v>57754</v>
+        <v>57839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>130024435</v>
       </c>
       <c r="B17" t="n">
-        <v>57735</v>
+        <v>57820</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>130024445</v>
       </c>
       <c r="B18" t="n">
-        <v>57735</v>
+        <v>57820</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
